--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Five-Aces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A64E7DB0-8782-4FB2-BDAD-12C487AB6B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234C5202-65D0-4AF3-8715-8860E73107D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4870,7 +4870,7 @@
         <v>46176.467592592591</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K151" t="s">
         <v>11</v>
@@ -4899,7 +4899,7 @@
         <v>46176.467592592591</v>
       </c>
       <c r="J152">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K152" t="s">
         <v>11</v>
@@ -4928,7 +4928,7 @@
         <v>46176.468287037038</v>
       </c>
       <c r="J153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K153" t="s">
         <v>11</v>
@@ -4957,7 +4957,7 @@
         <v>46176.468287037038</v>
       </c>
       <c r="J154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K154" t="s">
         <v>11</v>
@@ -4986,7 +4986,7 @@
         <v>46176.468287037038</v>
       </c>
       <c r="J155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K155" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Five-Aces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77A8A3DD-8754-4A43-9E47-2316F24BFC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F26D2F6-8F80-4113-BED0-B54E76E81E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="56">
   <si>
     <t>Company Name</t>
   </si>
@@ -89,6 +89,9 @@
     <t>Speed Management</t>
   </si>
   <si>
+    <t>Vehicle Inspections</t>
+  </si>
+  <si>
     <t>Winter Weather</t>
   </si>
   <si>
@@ -101,13 +104,22 @@
     <t>Space Management-Big 5</t>
   </si>
   <si>
+    <t>Distracted Driving</t>
+  </si>
+  <si>
     <t>Alert Driving</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
@@ -122,22 +134,10 @@
     <t>Safe Lifting for Commercial Drivers</t>
   </si>
   <si>
-    <t>Vehicle Inspections</t>
-  </si>
-  <si>
-    <t>Distracted Driving</t>
-  </si>
-  <si>
-    <t>Driver Health</t>
+    <t>Scene of an Accident</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Fire Extinguisher Training for CDL</t>
-  </si>
-  <si>
-    <t>Scene of an Accident</t>
   </si>
   <si>
     <t>Five Aces Specialized Transport LLC</t>
@@ -580,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -638,7 +638,7 @@
         <v>34</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>13</v>
@@ -667,7 +667,7 @@
         <v>35</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -696,7 +696,7 @@
         <v>36</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -725,7 +725,7 @@
         <v>37</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -754,7 +754,7 @@
         <v>38</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -783,7 +783,7 @@
         <v>39</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -812,7 +812,7 @@
         <v>40</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -841,7 +841,7 @@
         <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -870,7 +870,7 @@
         <v>34</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>13</v>
@@ -899,7 +899,7 @@
         <v>35</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -928,7 +928,7 @@
         <v>36</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -957,7 +957,7 @@
         <v>37</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -986,7 +986,7 @@
         <v>38</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -1015,7 +1015,7 @@
         <v>39</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1044,7 +1044,7 @@
         <v>42</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>13</v>
@@ -1073,7 +1073,7 @@
         <v>43</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1102,7 +1102,7 @@
         <v>41</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1131,7 +1131,7 @@
         <v>34</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>13</v>
@@ -1160,7 +1160,7 @@
         <v>35</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>12</v>
@@ -1184,7 +1184,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="1"/>
       <c r="M21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
@@ -1198,7 +1198,7 @@
         <v>36</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>13</v>
@@ -1227,7 +1227,7 @@
         <v>37</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1256,7 +1256,7 @@
         <v>38</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1285,7 +1285,7 @@
         <v>39</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1314,7 +1314,7 @@
         <v>42</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>14</v>
@@ -1338,7 +1338,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="1"/>
       <c r="M27" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
@@ -1352,7 +1352,7 @@
         <v>43</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1381,7 +1381,7 @@
         <v>41</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1613,7 +1613,7 @@
         <v>35</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>13</v>
@@ -1642,7 +1642,7 @@
         <v>36</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>13</v>
@@ -1671,7 +1671,7 @@
         <v>37</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>13</v>
@@ -1700,7 +1700,7 @@
         <v>38</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1729,7 +1729,7 @@
         <v>39</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1758,7 +1758,7 @@
         <v>44</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>13</v>
@@ -1787,7 +1787,7 @@
         <v>43</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>13</v>
@@ -1816,7 +1816,7 @@
         <v>41</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>13</v>
@@ -1845,7 +1845,7 @@
         <v>35</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1874,7 +1874,7 @@
         <v>36</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>13</v>
@@ -1903,7 +1903,7 @@
         <v>45</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>13</v>
@@ -1932,7 +1932,7 @@
         <v>37</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>13</v>
@@ -1961,7 +1961,7 @@
         <v>38</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
@@ -1990,7 +1990,7 @@
         <v>39</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>13</v>
@@ -2019,7 +2019,7 @@
         <v>44</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -2048,7 +2048,7 @@
         <v>43</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>13</v>
@@ -2077,7 +2077,7 @@
         <v>35</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>13</v>
@@ -2106,7 +2106,7 @@
         <v>36</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>13</v>
@@ -2135,7 +2135,7 @@
         <v>45</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2164,7 +2164,7 @@
         <v>37</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -2193,7 +2193,7 @@
         <v>38</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2222,7 +2222,7 @@
         <v>39</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>13</v>
@@ -2251,7 +2251,7 @@
         <v>44</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2280,7 +2280,7 @@
         <v>43</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2309,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2338,7 +2338,7 @@
         <v>36</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2367,7 +2367,7 @@
         <v>45</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2396,7 +2396,7 @@
         <v>37</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>12</v>
@@ -2420,7 +2420,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="1"/>
       <c r="M65" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
@@ -2434,7 +2434,7 @@
         <v>38</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2463,7 +2463,7 @@
         <v>39</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>13</v>
@@ -2492,7 +2492,7 @@
         <v>44</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>13</v>
@@ -2521,7 +2521,7 @@
         <v>43</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>13</v>
@@ -2550,7 +2550,7 @@
         <v>35</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>13</v>
@@ -2579,7 +2579,7 @@
         <v>36</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>13</v>
@@ -2608,7 +2608,7 @@
         <v>45</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2637,7 +2637,7 @@
         <v>37</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2666,7 +2666,7 @@
         <v>38</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2695,7 +2695,7 @@
         <v>39</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2724,7 +2724,7 @@
         <v>44</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>13</v>
@@ -2753,7 +2753,7 @@
         <v>43</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>13</v>
@@ -2782,7 +2782,7 @@
         <v>35</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>13</v>
@@ -2811,7 +2811,7 @@
         <v>36</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2840,7 +2840,7 @@
         <v>46</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2869,7 +2869,7 @@
         <v>37</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>13</v>
@@ -2898,7 +2898,7 @@
         <v>39</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>13</v>
@@ -2927,7 +2927,7 @@
         <v>44</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>13</v>
@@ -2956,7 +2956,7 @@
         <v>43</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>13</v>
@@ -2985,7 +2985,7 @@
         <v>35</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -3014,7 +3014,7 @@
         <v>36</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -3043,7 +3043,7 @@
         <v>46</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>13</v>
@@ -3072,7 +3072,7 @@
         <v>37</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -3101,7 +3101,7 @@
         <v>39</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -3130,7 +3130,7 @@
         <v>44</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -3159,7 +3159,7 @@
         <v>43</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -3188,7 +3188,7 @@
         <v>35</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -3217,7 +3217,7 @@
         <v>36</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -3246,7 +3246,7 @@
         <v>47</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>13</v>
@@ -3275,7 +3275,7 @@
         <v>48</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3304,7 +3304,7 @@
         <v>49</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>12</v>
@@ -3328,7 +3328,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="1"/>
       <c r="M97" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
@@ -3342,7 +3342,7 @@
         <v>37</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>13</v>
@@ -3371,7 +3371,7 @@
         <v>39</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>13</v>
@@ -3400,7 +3400,7 @@
         <v>43</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3429,7 +3429,7 @@
         <v>35</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>13</v>
@@ -3458,7 +3458,7 @@
         <v>36</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>13</v>
@@ -3487,7 +3487,7 @@
         <v>49</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3516,7 +3516,7 @@
         <v>37</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>13</v>
@@ -3545,7 +3545,7 @@
         <v>39</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>13</v>
@@ -3574,7 +3574,7 @@
         <v>43</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>13</v>
@@ -3603,7 +3603,7 @@
         <v>50</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>13</v>
@@ -3632,7 +3632,7 @@
         <v>35</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>13</v>
@@ -3661,7 +3661,7 @@
         <v>36</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>13</v>
@@ -3690,7 +3690,7 @@
         <v>51</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>12</v>
@@ -3714,7 +3714,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
       <c r="M111" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
@@ -3728,7 +3728,7 @@
         <v>49</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>13</v>
@@ -3757,7 +3757,7 @@
         <v>46</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>10</v>
@@ -3786,7 +3786,7 @@
         <v>52</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3815,7 +3815,7 @@
         <v>37</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3844,7 +3844,7 @@
         <v>39</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>13</v>
@@ -3873,7 +3873,7 @@
         <v>43</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>13</v>
@@ -3902,7 +3902,7 @@
         <v>50</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>13</v>
@@ -3931,7 +3931,7 @@
         <v>53</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -3960,7 +3960,7 @@
         <v>35</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3989,7 +3989,7 @@
         <v>36</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>13</v>
@@ -4018,7 +4018,7 @@
         <v>49</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>13</v>
@@ -4047,7 +4047,7 @@
         <v>37</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -4076,7 +4076,7 @@
         <v>39</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>13</v>
@@ -4105,7 +4105,7 @@
         <v>43</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -4134,7 +4134,7 @@
         <v>35</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>13</v>
@@ -4163,7 +4163,7 @@
         <v>36</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -4192,7 +4192,7 @@
         <v>49</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4221,7 +4221,7 @@
         <v>37</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -4250,7 +4250,7 @@
         <v>39</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4279,7 +4279,7 @@
         <v>54</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>13</v>
@@ -4308,7 +4308,7 @@
         <v>43</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>13</v>
@@ -4337,7 +4337,7 @@
         <v>35</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4366,7 +4366,7 @@
         <v>36</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>13</v>
@@ -4395,7 +4395,7 @@
         <v>49</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>13</v>
@@ -4424,7 +4424,7 @@
         <v>37</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>13</v>
@@ -4453,7 +4453,7 @@
         <v>39</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>13</v>
@@ -4482,7 +4482,7 @@
         <v>54</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>13</v>
@@ -4511,7 +4511,7 @@
         <v>43</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>13</v>
@@ -4540,7 +4540,7 @@
         <v>35</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>13</v>
@@ -4569,7 +4569,7 @@
         <v>49</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>13</v>
@@ -4598,7 +4598,7 @@
         <v>37</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4627,7 +4627,7 @@
         <v>39</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4656,7 +4656,7 @@
         <v>43</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4685,7 +4685,7 @@
         <v>35</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>13</v>
@@ -4714,7 +4714,7 @@
         <v>49</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>13</v>
@@ -4743,7 +4743,7 @@
         <v>37</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>13</v>
@@ -4772,7 +4772,7 @@
         <v>39</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4801,7 +4801,7 @@
         <v>43</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>13</v>
@@ -4859,7 +4859,7 @@
         <v>35</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>13</v>
@@ -4888,7 +4888,7 @@
         <v>49</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>13</v>
@@ -4917,7 +4917,7 @@
         <v>37</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>13</v>
@@ -4946,7 +4946,7 @@
         <v>39</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>13</v>
@@ -4975,7 +4975,7 @@
         <v>43</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>13</v>
@@ -4994,126 +4994,264 @@
       </c>
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H156" s="2"/>
-      <c r="I156" s="1"/>
-      <c r="J156" s="2"/>
-      <c r="K156" s="1"/>
+      <c r="D156" t="s">
+        <v>33</v>
+      </c>
+      <c r="E156">
+        <v>2756</v>
+      </c>
+      <c r="F156" t="s">
+        <v>35</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J156" s="2">
+        <v>0</v>
+      </c>
+      <c r="K156" s="1">
+        <v>46213.918055555558</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H157" s="2"/>
-      <c r="I157" s="1"/>
-      <c r="J157" s="2"/>
-      <c r="K157" s="1"/>
+      <c r="D157" t="s">
+        <v>33</v>
+      </c>
+      <c r="E157">
+        <v>4822</v>
+      </c>
+      <c r="F157" t="s">
+        <v>49</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J157" s="2">
+        <v>0</v>
+      </c>
+      <c r="K157" s="1">
+        <v>46213.918749999997</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H158" s="2"/>
-      <c r="I158" s="1"/>
-      <c r="J158" s="2"/>
-      <c r="K158" s="1"/>
+      <c r="D158" t="s">
+        <v>33</v>
+      </c>
+      <c r="E158">
+        <v>5755</v>
+      </c>
+      <c r="F158" t="s">
+        <v>55</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J158" s="2">
+        <v>0</v>
+      </c>
+      <c r="K158" s="1">
+        <v>46213.918749999997</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H159" s="2"/>
-      <c r="I159" s="1"/>
-      <c r="J159" s="2"/>
-      <c r="K159" s="1"/>
+      <c r="D159" t="s">
+        <v>33</v>
+      </c>
+      <c r="E159">
+        <v>2836</v>
+      </c>
+      <c r="F159" t="s">
+        <v>37</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J159" s="2">
+        <v>0</v>
+      </c>
+      <c r="K159" s="1">
+        <v>46213.919444444444</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H160" s="2"/>
-      <c r="I160" s="1"/>
-      <c r="J160" s="2"/>
-      <c r="K160" s="1"/>
-    </row>
-    <row r="161" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H161" s="2"/>
-      <c r="I161" s="1"/>
-      <c r="J161" s="2"/>
-      <c r="K161" s="1"/>
-    </row>
-    <row r="162" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D160" t="s">
+        <v>33</v>
+      </c>
+      <c r="E160">
+        <v>2755</v>
+      </c>
+      <c r="F160" t="s">
+        <v>39</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J160" s="2">
+        <v>0</v>
+      </c>
+      <c r="K160" s="1">
+        <v>46213.919444444444</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D161" t="s">
+        <v>33</v>
+      </c>
+      <c r="E161">
+        <v>2907</v>
+      </c>
+      <c r="F161" t="s">
+        <v>43</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J161" s="2">
+        <v>0</v>
+      </c>
+      <c r="K161" s="1">
+        <v>46213.920138888891</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H162" s="2"/>
       <c r="I162" s="1"/>
       <c r="J162" s="2"/>
       <c r="K162" s="1"/>
     </row>
-    <row r="163" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H163" s="2"/>
       <c r="I163" s="1"/>
       <c r="J163" s="2"/>
       <c r="K163" s="1"/>
     </row>
-    <row r="164" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H164" s="2"/>
       <c r="I164" s="1"/>
       <c r="J164" s="2"/>
       <c r="K164" s="1"/>
     </row>
-    <row r="165" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H165" s="2"/>
       <c r="I165" s="1"/>
       <c r="J165" s="2"/>
       <c r="K165" s="1"/>
     </row>
-    <row r="166" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H166" s="2"/>
       <c r="I166" s="1"/>
       <c r="J166" s="2"/>
       <c r="K166" s="1"/>
     </row>
-    <row r="167" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H167" s="2"/>
       <c r="I167" s="1"/>
       <c r="J167" s="2"/>
       <c r="K167" s="1"/>
     </row>
-    <row r="168" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H168" s="2"/>
       <c r="I168" s="1"/>
       <c r="J168" s="2"/>
       <c r="K168" s="1"/>
     </row>
-    <row r="169" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H169" s="2"/>
       <c r="I169" s="1"/>
       <c r="J169" s="2"/>
       <c r="K169" s="1"/>
     </row>
-    <row r="170" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H170" s="2"/>
       <c r="I170" s="1"/>
       <c r="J170" s="2"/>
       <c r="K170" s="1"/>
     </row>
-    <row r="171" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H171" s="2"/>
       <c r="I171" s="1"/>
       <c r="J171" s="2"/>
       <c r="K171" s="1"/>
     </row>
-    <row r="172" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H172" s="2"/>
       <c r="I172" s="1"/>
       <c r="J172" s="2"/>
       <c r="K172" s="1"/>
     </row>
-    <row r="173" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H173" s="2"/>
       <c r="I173" s="1"/>
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
       <c r="K174" s="1"/>
     </row>
-    <row r="175" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H175" s="2"/>
       <c r="I175" s="1"/>
       <c r="J175" s="2"/>
       <c r="K175" s="1"/>
     </row>
-    <row r="176" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H176" s="2"/>
       <c r="I176" s="1"/>
       <c r="J176" s="2"/>
@@ -8241,6 +8379,7 @@
     <row r="697" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H697" s="2"/>
       <c r="I697" s="1"/>
+      <c r="J697" s="2"/>
       <c r="K697" s="1"/>
     </row>
     <row r="698" spans="8:11" x14ac:dyDescent="0.3">
@@ -8550,6 +8689,7 @@
     <row r="749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H749" s="2"/>
       <c r="I749" s="1"/>
+      <c r="J749" s="2"/>
       <c r="K749" s="1"/>
     </row>
     <row r="750" spans="8:11" x14ac:dyDescent="0.3">
@@ -8639,6 +8779,7 @@
     <row r="764" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H764" s="2"/>
       <c r="I764" s="1"/>
+      <c r="J764" s="2"/>
       <c r="K764" s="1"/>
     </row>
     <row r="765" spans="8:11" x14ac:dyDescent="0.3">
@@ -8762,6 +8903,7 @@
     <row r="785" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H785" s="2"/>
       <c r="I785" s="1"/>
+      <c r="J785" s="2"/>
       <c r="K785" s="1"/>
     </row>
     <row r="786" spans="8:11" x14ac:dyDescent="0.3">
@@ -8814,6 +8956,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -8888,6 +9031,7 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
@@ -42396,7 +42540,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Five-Aces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F26D2F6-8F80-4113-BED0-B54E76E81E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B9546FF-690E-4FE0-AAC4-D096A4CB2647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -86,7 +86,7 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
   </si>
   <si>
     <t>Vehicle Inspections</t>
@@ -101,37 +101,37 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Space Management-Big 5</t>
+    <t>Distracted Driving</t>
   </si>
   <si>
-    <t>Distracted Driving</t>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Alert Driving</t>
   </si>
   <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
+    <t>Space Management-Big 5</t>
+  </si>
+  <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Speed Mangement-C</t>
-  </si>
-  <si>
-    <t>Safe Lifting for Commercial Drivers</t>
   </si>
   <si>
     <t>Scene of an Accident</t>
@@ -580,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -1184,7 +1184,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="1"/>
       <c r="M21" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
@@ -1338,7 +1338,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="1"/>
       <c r="M27" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
@@ -1410,7 +1410,7 @@
         <v>35</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>13</v>
@@ -1439,7 +1439,7 @@
         <v>36</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>13</v>
@@ -1468,7 +1468,7 @@
         <v>37</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -1497,7 +1497,7 @@
         <v>38</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1526,7 +1526,7 @@
         <v>39</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>13</v>
@@ -1555,7 +1555,7 @@
         <v>43</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1584,7 +1584,7 @@
         <v>41</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1613,7 +1613,7 @@
         <v>35</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>13</v>
@@ -1642,7 +1642,7 @@
         <v>36</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>13</v>
@@ -1671,7 +1671,7 @@
         <v>37</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>13</v>
@@ -1700,7 +1700,7 @@
         <v>38</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1729,7 +1729,7 @@
         <v>39</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1758,7 +1758,7 @@
         <v>44</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>13</v>
@@ -1787,7 +1787,7 @@
         <v>43</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>13</v>
@@ -1816,7 +1816,7 @@
         <v>41</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>13</v>
@@ -2077,7 +2077,7 @@
         <v>35</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>13</v>
@@ -2106,7 +2106,7 @@
         <v>36</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>13</v>
@@ -2135,7 +2135,7 @@
         <v>45</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2164,7 +2164,7 @@
         <v>37</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -2193,7 +2193,7 @@
         <v>38</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2222,7 +2222,7 @@
         <v>39</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>13</v>
@@ -2251,7 +2251,7 @@
         <v>44</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2280,7 +2280,7 @@
         <v>43</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2309,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2338,7 +2338,7 @@
         <v>36</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2367,7 +2367,7 @@
         <v>45</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2396,7 +2396,7 @@
         <v>37</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>12</v>
@@ -2420,7 +2420,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="1"/>
       <c r="M65" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
@@ -2434,7 +2434,7 @@
         <v>38</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2463,7 +2463,7 @@
         <v>39</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>13</v>
@@ -2492,7 +2492,7 @@
         <v>44</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>13</v>
@@ -2521,7 +2521,7 @@
         <v>43</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>13</v>
@@ -2985,7 +2985,7 @@
         <v>35</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -3014,7 +3014,7 @@
         <v>36</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -3043,7 +3043,7 @@
         <v>46</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>13</v>
@@ -3072,7 +3072,7 @@
         <v>37</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -3101,7 +3101,7 @@
         <v>39</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -3130,7 +3130,7 @@
         <v>44</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -3159,7 +3159,7 @@
         <v>43</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -3328,7 +3328,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="1"/>
       <c r="M97" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
@@ -3714,7 +3714,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
       <c r="M111" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
@@ -3960,7 +3960,7 @@
         <v>35</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3989,7 +3989,7 @@
         <v>36</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>13</v>
@@ -4018,7 +4018,7 @@
         <v>49</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>13</v>
@@ -4047,7 +4047,7 @@
         <v>37</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -4076,7 +4076,7 @@
         <v>39</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>13</v>
@@ -4105,7 +4105,7 @@
         <v>43</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -4134,7 +4134,7 @@
         <v>35</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>13</v>
@@ -4163,7 +4163,7 @@
         <v>36</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -4192,7 +4192,7 @@
         <v>49</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4221,7 +4221,7 @@
         <v>37</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -4250,7 +4250,7 @@
         <v>39</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4279,7 +4279,7 @@
         <v>54</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>13</v>
@@ -4308,7 +4308,7 @@
         <v>43</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>13</v>
@@ -4337,7 +4337,7 @@
         <v>35</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4366,7 +4366,7 @@
         <v>36</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>13</v>
@@ -4395,7 +4395,7 @@
         <v>49</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>13</v>
@@ -4424,7 +4424,7 @@
         <v>37</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>13</v>
@@ -4453,7 +4453,7 @@
         <v>39</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>13</v>
@@ -4482,7 +4482,7 @@
         <v>54</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>13</v>
@@ -4511,7 +4511,7 @@
         <v>43</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>13</v>
@@ -4540,7 +4540,7 @@
         <v>35</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>13</v>
@@ -4569,7 +4569,7 @@
         <v>49</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>13</v>
@@ -4598,7 +4598,7 @@
         <v>37</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4627,7 +4627,7 @@
         <v>39</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4656,7 +4656,7 @@
         <v>43</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4830,7 +4830,7 @@
         <v>55</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>10</v>
@@ -4859,7 +4859,7 @@
         <v>35</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>13</v>
@@ -4888,7 +4888,7 @@
         <v>49</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>13</v>
@@ -4917,7 +4917,7 @@
         <v>37</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>13</v>
@@ -4946,7 +4946,7 @@
         <v>39</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>13</v>
@@ -4975,7 +4975,7 @@
         <v>43</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>13</v>
@@ -5004,7 +5004,7 @@
         <v>35</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>13</v>
@@ -5033,7 +5033,7 @@
         <v>49</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>13</v>
@@ -5062,7 +5062,7 @@
         <v>55</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -5091,7 +5091,7 @@
         <v>37</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>13</v>
@@ -5120,7 +5120,7 @@
         <v>39</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>13</v>
@@ -5149,7 +5149,7 @@
         <v>43</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>13</v>
@@ -8886,6 +8886,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -8915,6 +8916,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -8980,6 +8982,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -9003,6 +9006,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -9020,6 +9024,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -9037,6 +9042,7 @@
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -9156,6 +9162,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -9239,6 +9246,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -9262,6 +9270,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -9273,6 +9282,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -9284,6 +9294,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -9331,6 +9342,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -9384,6 +9396,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -9556,6 +9569,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -9567,6 +9581,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -9644,6 +9659,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -9661,6 +9677,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -9708,6 +9725,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -9820,6 +9838,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -9879,6 +9898,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -9890,6 +9910,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -9961,6 +9982,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -10013,6 +10035,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -10089,11 +10112,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -10153,6 +10178,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -10164,6 +10190,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -10175,11 +10202,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -10233,6 +10262,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -10249,6 +10279,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -10272,6 +10303,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -10289,6 +10321,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -10335,11 +10368,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -10381,11 +10416,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -10403,6 +10440,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -10414,6 +10452,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -10425,6 +10464,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -10442,6 +10482,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -10519,6 +10560,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -10548,6 +10590,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -10559,16 +10602,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -10580,16 +10626,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -10601,11 +10650,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -10629,6 +10680,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -10670,6 +10722,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -10699,21 +10752,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -10725,6 +10782,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -10742,6 +10800,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -10781,11 +10840,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -10833,6 +10894,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -10862,6 +10924,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -10938,6 +11001,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -10984,6 +11048,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -11019,11 +11084,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -11040,6 +11107,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -11050,6 +11118,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -11085,6 +11154,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -11096,6 +11166,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -11107,6 +11178,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -11118,6 +11190,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -11129,6 +11202,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -11170,6 +11244,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -11187,6 +11262,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -11204,6 +11280,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -11245,6 +11322,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -11268,6 +11346,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -11314,6 +11393,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -11349,6 +11429,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -11372,6 +11453,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -11412,6 +11494,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -11429,11 +11512,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -11492,6 +11577,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -11508,6 +11594,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -11519,6 +11606,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -11530,11 +11618,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -11570,6 +11660,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -11622,6 +11713,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -11632,6 +11724,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -11647,6 +11740,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -11670,16 +11764,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -11750,6 +11847,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -11761,6 +11859,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -11861,6 +11960,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -11917,6 +12018,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -11940,6 +12042,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -12064,6 +12167,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -12222,6 +12326,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -12239,6 +12344,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -12279,6 +12385,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -12611,6 +12718,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -12699,6 +12807,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -12792,6 +12901,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -12851,11 +12961,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -12907,6 +13019,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -12948,6 +13061,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -12992,6 +13106,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -13038,11 +13153,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -13240,6 +13357,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -13269,6 +13387,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -13284,6 +13404,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -13343,6 +13464,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -13414,6 +13536,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -13455,6 +13578,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -13573,6 +13697,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -13637,6 +13762,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -13761,6 +13887,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -13987,6 +14114,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -14104,6 +14232,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -14187,6 +14316,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -14246,6 +14376,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -14269,6 +14400,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -14316,6 +14448,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -14375,6 +14508,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -14398,6 +14532,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -14415,6 +14550,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -14498,6 +14634,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -14689,6 +14826,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -42545,6 +42683,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -42552,6 +42691,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -42559,6 +42699,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -42574,6 +42715,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -42583,6 +42725,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -42590,9 +42733,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -42600,12 +42749,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -42613,12 +42765,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -42630,9 +42785,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -42647,6 +42804,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -42673,6 +42831,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -42683,7 +42842,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -42691,6 +42855,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -42702,6 +42867,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -42709,6 +42875,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -42723,13 +42890,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -42740,15 +42913,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -42764,6 +42940,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -42782,6 +42959,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -42793,6 +42971,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -42810,18 +42989,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -42850,6 +43034,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -42857,9 +43042,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -42882,12 +43069,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -42902,9 +43092,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -42920,12 +43112,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -42946,6 +43140,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -42957,9 +43152,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -42971,6 +43168,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -43010,9 +43208,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -43020,9 +43220,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -43033,6 +43235,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -43040,18 +43243,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -43059,6 +43270,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -43069,6 +43281,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -43095,15 +43308,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -43125,6 +43342,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -43132,9 +43350,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -43142,6 +43362,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -43153,6 +43374,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -43167,6 +43389,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -43176,6 +43402,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -43187,6 +43414,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -43197,10 +43425,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -43208,6 +43441,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -43222,6 +43456,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -43244,6 +43479,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -43263,25 +43499,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -43289,6 +43537,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -43296,15 +43545,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -43318,6 +43574,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -43336,9 +43593,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -43346,9 +43605,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -43356,6 +43617,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -43372,10 +43634,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Five-Aces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEE640E1-15CE-4273-856F-2DA7D9BA23C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{280C9999-F605-4766-B8C6-6A903720F89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="57">
   <si>
     <t>Company Name</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>Speed Mangement-C</t>
+  </si>
+  <si>
+    <t>Dangers of Distracted Driving</t>
   </si>
   <si>
     <t>Scene of an Accident</t>
@@ -580,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -595,47 +598,47 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2">
         <v>2837</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
@@ -656,15 +659,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>2756</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -685,15 +688,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>2754</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
@@ -714,15 +717,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5">
         <v>2836</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -743,15 +746,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>2838</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
@@ -772,15 +775,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>2755</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
@@ -801,15 +804,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>2860</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
@@ -830,15 +833,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>2797</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
@@ -859,15 +862,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>2837</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -888,15 +891,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>2756</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -917,15 +920,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>2754</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -946,15 +949,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>2836</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -975,15 +978,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>2838</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -1004,15 +1007,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15">
         <v>2755</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -1033,15 +1036,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>2871</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -1064,13 +1067,13 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17">
         <v>2907</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -1093,13 +1096,13 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18">
         <v>2797</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -1122,13 +1125,13 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>2837</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
         <v>22</v>
@@ -1151,13 +1154,13 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20">
         <v>2756</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
         <v>22</v>
@@ -1188,13 +1191,13 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22">
         <v>2754</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F22" t="s">
         <v>22</v>
@@ -1217,13 +1220,13 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23">
         <v>2836</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
         <v>22</v>
@@ -1246,13 +1249,13 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24">
         <v>2838</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s">
         <v>22</v>
@@ -1275,13 +1278,13 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25">
         <v>2755</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F25" t="s">
         <v>22</v>
@@ -1304,13 +1307,13 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>2871</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
         <v>22</v>
@@ -1341,13 +1344,13 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C28">
         <v>2907</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F28" t="s">
         <v>22</v>
@@ -1370,13 +1373,13 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C29">
         <v>2797</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F29" t="s">
         <v>22</v>
@@ -1399,13 +1402,13 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C30">
         <v>2756</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F30" t="s">
         <v>23</v>
@@ -1428,13 +1431,13 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31">
         <v>2754</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F31" t="s">
         <v>23</v>
@@ -1457,13 +1460,13 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>2836</v>
       </c>
       <c r="D32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s">
         <v>23</v>
@@ -1486,13 +1489,13 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C33">
         <v>2838</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s">
         <v>23</v>
@@ -1515,13 +1518,13 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C34">
         <v>2755</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F34" t="s">
         <v>23</v>
@@ -1544,13 +1547,13 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C35">
         <v>2907</v>
       </c>
       <c r="D35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F35" t="s">
         <v>23</v>
@@ -1573,13 +1576,13 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C36">
         <v>2797</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F36" t="s">
         <v>23</v>
@@ -1602,13 +1605,13 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C37">
         <v>2756</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -1631,13 +1634,13 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C38">
         <v>2754</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -1660,13 +1663,13 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C39">
         <v>2836</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -1689,13 +1692,13 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C40">
         <v>2838</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -1718,13 +1721,13 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C41">
         <v>2755</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -1747,13 +1750,13 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C42">
         <v>3128</v>
       </c>
       <c r="D42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -1776,13 +1779,13 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C43">
         <v>2907</v>
       </c>
       <c r="D43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -1805,13 +1808,13 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C44">
         <v>2797</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -1834,13 +1837,13 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C45">
         <v>2756</v>
       </c>
       <c r="D45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F45" t="s">
         <v>16</v>
@@ -1863,13 +1866,13 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C46">
         <v>2754</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
@@ -1892,13 +1895,13 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C47">
         <v>3235</v>
       </c>
       <c r="D47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F47" t="s">
         <v>16</v>
@@ -1921,13 +1924,13 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C48">
         <v>2836</v>
       </c>
       <c r="D48" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -1950,13 +1953,13 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C49">
         <v>2838</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
@@ -1979,13 +1982,13 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C50">
         <v>2755</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -2008,13 +2011,13 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C51">
         <v>3128</v>
       </c>
       <c r="D51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
@@ -2037,13 +2040,13 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C52">
         <v>2907</v>
       </c>
       <c r="D52" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
@@ -2066,13 +2069,13 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C53">
         <v>2756</v>
       </c>
       <c r="D53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F53" t="s">
         <v>21</v>
@@ -2095,13 +2098,13 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C54">
         <v>2754</v>
       </c>
       <c r="D54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F54" t="s">
         <v>21</v>
@@ -2124,13 +2127,13 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C55">
         <v>3235</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F55" t="s">
         <v>21</v>
@@ -2153,13 +2156,13 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C56">
         <v>2836</v>
       </c>
       <c r="D56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F56" t="s">
         <v>21</v>
@@ -2182,13 +2185,13 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C57">
         <v>2838</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F57" t="s">
         <v>21</v>
@@ -2211,13 +2214,13 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C58">
         <v>2755</v>
       </c>
       <c r="D58" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F58" t="s">
         <v>21</v>
@@ -2240,13 +2243,13 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C59">
         <v>3128</v>
       </c>
       <c r="D59" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F59" t="s">
         <v>21</v>
@@ -2269,13 +2272,13 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C60">
         <v>2907</v>
       </c>
       <c r="D60" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F60" t="s">
         <v>21</v>
@@ -2298,13 +2301,13 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C61">
         <v>2756</v>
       </c>
       <c r="D61" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F61" t="s">
         <v>20</v>
@@ -2327,13 +2330,13 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C62">
         <v>2754</v>
       </c>
       <c r="D62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F62" t="s">
         <v>20</v>
@@ -2356,13 +2359,13 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C63">
         <v>3235</v>
       </c>
       <c r="D63" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F63" t="s">
         <v>20</v>
@@ -2385,13 +2388,13 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C64">
         <v>2836</v>
       </c>
       <c r="D64" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F64" t="s">
         <v>20</v>
@@ -2422,13 +2425,13 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C66">
         <v>2838</v>
       </c>
       <c r="D66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F66" t="s">
         <v>20</v>
@@ -2451,13 +2454,13 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C67">
         <v>2755</v>
       </c>
       <c r="D67" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F67" t="s">
         <v>20</v>
@@ -2480,13 +2483,13 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C68">
         <v>3128</v>
       </c>
       <c r="D68" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F68" t="s">
         <v>20</v>
@@ -2509,13 +2512,13 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C69">
         <v>2907</v>
       </c>
       <c r="D69" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F69" t="s">
         <v>20</v>
@@ -2538,16 +2541,16 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C70">
         <v>2756</v>
       </c>
       <c r="D70" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F70" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G70" t="s">
         <v>13</v>
@@ -2567,16 +2570,16 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C71">
         <v>2754</v>
       </c>
       <c r="D71" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F71" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G71" t="s">
         <v>13</v>
@@ -2596,16 +2599,16 @@
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C72">
         <v>3235</v>
       </c>
       <c r="D72" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F72" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G72" t="s">
         <v>13</v>
@@ -2625,16 +2628,16 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C73">
         <v>2836</v>
       </c>
       <c r="D73" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F73" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G73" t="s">
         <v>13</v>
@@ -2654,16 +2657,16 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C74">
         <v>2838</v>
       </c>
       <c r="D74" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2683,16 +2686,16 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C75">
         <v>2755</v>
       </c>
       <c r="D75" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G75" t="s">
         <v>13</v>
@@ -2712,16 +2715,16 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C76">
         <v>3128</v>
       </c>
       <c r="D76" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F76" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G76" t="s">
         <v>13</v>
@@ -2741,16 +2744,16 @@
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C77">
         <v>2907</v>
       </c>
       <c r="D77" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F77" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G77" t="s">
         <v>13</v>
@@ -2770,16 +2773,16 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C78">
         <v>2756</v>
       </c>
       <c r="D78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F78" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G78" t="s">
         <v>13</v>
@@ -2799,16 +2802,16 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C79">
         <v>2754</v>
       </c>
       <c r="D79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F79" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G79" t="s">
         <v>13</v>
@@ -2828,16 +2831,16 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C80">
         <v>3834</v>
       </c>
       <c r="D80" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F80" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G80" t="s">
         <v>10</v>
@@ -2857,16 +2860,16 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C81">
         <v>2836</v>
       </c>
       <c r="D81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F81" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G81" t="s">
         <v>13</v>
@@ -2886,16 +2889,16 @@
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C82">
         <v>2755</v>
       </c>
       <c r="D82" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G82" t="s">
         <v>13</v>
@@ -2915,16 +2918,16 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C83">
         <v>3128</v>
       </c>
       <c r="D83" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F83" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G83" t="s">
         <v>13</v>
@@ -2944,16 +2947,16 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C84">
         <v>2907</v>
       </c>
       <c r="D84" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G84" t="s">
         <v>13</v>
@@ -2973,13 +2976,13 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C85">
         <v>2756</v>
       </c>
       <c r="D85" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F85" t="s">
         <v>24</v>
@@ -3002,13 +3005,13 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C86">
         <v>2754</v>
       </c>
       <c r="D86" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F86" t="s">
         <v>24</v>
@@ -3031,13 +3034,13 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C87">
         <v>3834</v>
       </c>
       <c r="D87" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F87" t="s">
         <v>24</v>
@@ -3060,13 +3063,13 @@
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C88">
         <v>2836</v>
       </c>
       <c r="D88" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F88" t="s">
         <v>24</v>
@@ -3089,13 +3092,13 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C89">
         <v>2755</v>
       </c>
       <c r="D89" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F89" t="s">
         <v>24</v>
@@ -3118,13 +3121,13 @@
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C90">
         <v>3128</v>
       </c>
       <c r="D90" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F90" t="s">
         <v>24</v>
@@ -3147,13 +3150,13 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C91">
         <v>2907</v>
       </c>
       <c r="D91" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F91" t="s">
         <v>24</v>
@@ -3176,13 +3179,13 @@
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C92">
         <v>2756</v>
       </c>
       <c r="D92" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
         <v>19</v>
@@ -3205,13 +3208,13 @@
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C93">
         <v>2754</v>
       </c>
       <c r="D93" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F93" t="s">
         <v>19</v>
@@ -3234,13 +3237,13 @@
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C94">
         <v>4814</v>
       </c>
       <c r="D94" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F94" t="s">
         <v>19</v>
@@ -3263,13 +3266,13 @@
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C95">
         <v>4821</v>
       </c>
       <c r="D95" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F95" t="s">
         <v>19</v>
@@ -3292,13 +3295,13 @@
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C96">
         <v>4822</v>
       </c>
       <c r="D96" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F96" t="s">
         <v>19</v>
@@ -3329,13 +3332,13 @@
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C98">
         <v>2836</v>
       </c>
       <c r="D98" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F98" t="s">
         <v>19</v>
@@ -3358,13 +3361,13 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C99">
         <v>2755</v>
       </c>
       <c r="D99" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F99" t="s">
         <v>19</v>
@@ -3387,13 +3390,13 @@
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C100">
         <v>2907</v>
       </c>
       <c r="D100" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F100" t="s">
         <v>19</v>
@@ -3416,13 +3419,13 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C101">
         <v>2756</v>
       </c>
       <c r="D101" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F101" t="s">
         <v>17</v>
@@ -3445,13 +3448,13 @@
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C102">
         <v>2754</v>
       </c>
       <c r="D102" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F102" t="s">
         <v>17</v>
@@ -3474,13 +3477,13 @@
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C103">
         <v>4822</v>
       </c>
       <c r="D103" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F103" t="s">
         <v>17</v>
@@ -3503,13 +3506,13 @@
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C104">
         <v>2836</v>
       </c>
       <c r="D104" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F104" t="s">
         <v>17</v>
@@ -3532,13 +3535,13 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C105">
         <v>2755</v>
       </c>
       <c r="D105" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F105" t="s">
         <v>17</v>
@@ -3561,13 +3564,13 @@
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C106">
         <v>2907</v>
       </c>
       <c r="D106" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F106" t="s">
         <v>17</v>
@@ -3590,13 +3593,13 @@
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C107">
         <v>4937</v>
       </c>
       <c r="D107" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F107" t="s">
         <v>17</v>
@@ -3619,13 +3622,13 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C108">
         <v>2756</v>
       </c>
       <c r="D108" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F108" t="s">
         <v>18</v>
@@ -3648,13 +3651,13 @@
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C109">
         <v>2754</v>
       </c>
       <c r="D109" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F109" t="s">
         <v>18</v>
@@ -3677,13 +3680,13 @@
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C110">
         <v>5026</v>
       </c>
       <c r="D110" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F110" t="s">
         <v>18</v>
@@ -3714,13 +3717,13 @@
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C112">
         <v>4822</v>
       </c>
       <c r="D112" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F112" t="s">
         <v>18</v>
@@ -3743,13 +3746,13 @@
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C113">
         <v>3834</v>
       </c>
       <c r="D113" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F113" t="s">
         <v>18</v>
@@ -3772,13 +3775,13 @@
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C114">
         <v>5029</v>
       </c>
       <c r="D114" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F114" t="s">
         <v>18</v>
@@ -3801,13 +3804,13 @@
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C115">
         <v>2836</v>
       </c>
       <c r="D115" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F115" t="s">
         <v>18</v>
@@ -3830,13 +3833,13 @@
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C116">
         <v>2755</v>
       </c>
       <c r="D116" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F116" t="s">
         <v>18</v>
@@ -3859,13 +3862,13 @@
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C117">
         <v>2907</v>
       </c>
       <c r="D117" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F117" t="s">
         <v>18</v>
@@ -3888,13 +3891,13 @@
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C118">
         <v>4937</v>
       </c>
       <c r="D118" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F118" t="s">
         <v>18</v>
@@ -3917,13 +3920,13 @@
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C119">
         <v>5006</v>
       </c>
       <c r="D119" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F119" t="s">
         <v>18</v>
@@ -3946,13 +3949,13 @@
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C120">
         <v>2756</v>
       </c>
       <c r="D120" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F120" t="s">
         <v>26</v>
@@ -3975,13 +3978,13 @@
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C121">
         <v>2754</v>
       </c>
       <c r="D121" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F121" t="s">
         <v>26</v>
@@ -4004,13 +4007,13 @@
     </row>
     <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C122">
         <v>4822</v>
       </c>
       <c r="D122" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F122" t="s">
         <v>26</v>
@@ -4033,13 +4036,13 @@
     </row>
     <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C123">
         <v>2836</v>
       </c>
       <c r="D123" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F123" t="s">
         <v>26</v>
@@ -4062,13 +4065,13 @@
     </row>
     <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C124">
         <v>2755</v>
       </c>
       <c r="D124" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F124" t="s">
         <v>26</v>
@@ -4091,13 +4094,13 @@
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C125">
         <v>2907</v>
       </c>
       <c r="D125" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F125" t="s">
         <v>26</v>
@@ -4120,13 +4123,13 @@
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C126">
         <v>2756</v>
       </c>
       <c r="D126" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F126" t="s">
         <v>27</v>
@@ -4149,13 +4152,13 @@
     </row>
     <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C127">
         <v>2754</v>
       </c>
       <c r="D127" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F127" t="s">
         <v>27</v>
@@ -4178,13 +4181,13 @@
     </row>
     <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C128">
         <v>4822</v>
       </c>
       <c r="D128" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F128" t="s">
         <v>27</v>
@@ -4207,13 +4210,13 @@
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C129">
         <v>2836</v>
       </c>
       <c r="D129" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F129" t="s">
         <v>27</v>
@@ -4236,13 +4239,13 @@
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C130">
         <v>2755</v>
       </c>
       <c r="D130" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F130" t="s">
         <v>27</v>
@@ -4265,13 +4268,13 @@
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C131">
         <v>5174</v>
       </c>
       <c r="D131" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F131" t="s">
         <v>27</v>
@@ -4294,13 +4297,13 @@
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C132">
         <v>2907</v>
       </c>
       <c r="D132" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F132" t="s">
         <v>27</v>
@@ -4323,13 +4326,13 @@
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C133">
         <v>2756</v>
       </c>
       <c r="D133" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -4352,13 +4355,13 @@
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C134">
         <v>2754</v>
       </c>
       <c r="D134" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -4381,13 +4384,13 @@
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C135">
         <v>4822</v>
       </c>
       <c r="D135" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -4410,13 +4413,13 @@
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C136">
         <v>2836</v>
       </c>
       <c r="D136" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -4439,13 +4442,13 @@
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C137">
         <v>2755</v>
       </c>
       <c r="D137" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -4468,13 +4471,13 @@
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C138">
         <v>5174</v>
       </c>
       <c r="D138" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -4497,13 +4500,13 @@
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C139">
         <v>2907</v>
       </c>
       <c r="D139" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -4526,13 +4529,13 @@
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C140">
         <v>2756</v>
       </c>
       <c r="D140" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F140" t="s">
         <v>29</v>
@@ -4555,13 +4558,13 @@
     </row>
     <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C141">
         <v>4822</v>
       </c>
       <c r="D141" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F141" t="s">
         <v>29</v>
@@ -4584,13 +4587,13 @@
     </row>
     <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C142">
         <v>2836</v>
       </c>
       <c r="D142" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F142" t="s">
         <v>29</v>
@@ -4613,13 +4616,13 @@
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C143">
         <v>2755</v>
       </c>
       <c r="D143" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F143" t="s">
         <v>29</v>
@@ -4642,13 +4645,13 @@
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C144">
         <v>2907</v>
       </c>
       <c r="D144" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F144" t="s">
         <v>29</v>
@@ -4671,13 +4674,13 @@
     </row>
     <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C145">
         <v>2756</v>
       </c>
       <c r="D145" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F145" t="s">
         <v>19</v>
@@ -4700,13 +4703,13 @@
     </row>
     <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C146">
         <v>4822</v>
       </c>
       <c r="D146" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F146" t="s">
         <v>19</v>
@@ -4729,13 +4732,13 @@
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C147">
         <v>2836</v>
       </c>
       <c r="D147" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F147" t="s">
         <v>19</v>
@@ -4758,13 +4761,13 @@
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C148">
         <v>2755</v>
       </c>
       <c r="D148" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F148" t="s">
         <v>19</v>
@@ -4787,13 +4790,13 @@
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C149">
         <v>2907</v>
       </c>
       <c r="D149" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F149" t="s">
         <v>19</v>
@@ -4816,13 +4819,13 @@
     </row>
     <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C150">
         <v>5755</v>
       </c>
       <c r="D150" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F150" t="s">
         <v>23</v>
@@ -4845,13 +4848,13 @@
     </row>
     <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C151">
         <v>2756</v>
       </c>
       <c r="D151" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F151" t="s">
         <v>30</v>
@@ -4874,13 +4877,13 @@
     </row>
     <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C152">
         <v>4822</v>
       </c>
       <c r="D152" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F152" t="s">
         <v>30</v>
@@ -4903,13 +4906,13 @@
     </row>
     <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C153">
         <v>2836</v>
       </c>
       <c r="D153" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F153" t="s">
         <v>30</v>
@@ -4932,13 +4935,13 @@
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C154">
         <v>2755</v>
       </c>
       <c r="D154" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F154" t="s">
         <v>30</v>
@@ -4961,13 +4964,13 @@
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C155">
         <v>2907</v>
       </c>
       <c r="D155" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F155" t="s">
         <v>30</v>
@@ -4990,13 +4993,13 @@
     </row>
     <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C156">
         <v>2756</v>
       </c>
       <c r="D156" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F156" t="s">
         <v>21</v>
@@ -5019,13 +5022,13 @@
     </row>
     <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C157">
         <v>4822</v>
       </c>
       <c r="D157" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F157" t="s">
         <v>21</v>
@@ -5048,13 +5051,13 @@
     </row>
     <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C158">
         <v>5755</v>
       </c>
       <c r="D158" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F158" t="s">
         <v>21</v>
@@ -5077,13 +5080,13 @@
     </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C159">
         <v>2836</v>
       </c>
       <c r="D159" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F159" t="s">
         <v>21</v>
@@ -5106,13 +5109,13 @@
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C160">
         <v>2755</v>
       </c>
       <c r="D160" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F160" t="s">
         <v>21</v>
@@ -5135,13 +5138,13 @@
     </row>
     <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C161">
         <v>2907</v>
       </c>
       <c r="D161" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F161" t="s">
         <v>21</v>
@@ -5163,40 +5166,178 @@
       </c>
     </row>
     <row r="162" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H162" s="2"/>
-      <c r="I162" s="1"/>
-      <c r="J162" s="2"/>
-      <c r="K162" s="1"/>
+      <c r="B162" t="s">
+        <v>34</v>
+      </c>
+      <c r="C162">
+        <v>2756</v>
+      </c>
+      <c r="D162" t="s">
+        <v>36</v>
+      </c>
+      <c r="F162" t="s">
+        <v>31</v>
+      </c>
+      <c r="G162" t="s">
+        <v>13</v>
+      </c>
+      <c r="H162" s="2">
+        <v>0</v>
+      </c>
+      <c r="I162" s="1">
+        <v>46237.764467592591</v>
+      </c>
+      <c r="J162" s="2">
+        <v>0</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="163" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H163" s="2"/>
-      <c r="I163" s="1"/>
-      <c r="J163" s="2"/>
-      <c r="K163" s="1"/>
+      <c r="B163" t="s">
+        <v>34</v>
+      </c>
+      <c r="C163">
+        <v>4822</v>
+      </c>
+      <c r="D163" t="s">
+        <v>50</v>
+      </c>
+      <c r="F163" t="s">
+        <v>31</v>
+      </c>
+      <c r="G163" t="s">
+        <v>13</v>
+      </c>
+      <c r="H163" s="2">
+        <v>0</v>
+      </c>
+      <c r="I163" s="1">
+        <v>46237.764467592591</v>
+      </c>
+      <c r="J163" s="2">
+        <v>0</v>
+      </c>
+      <c r="K163" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="164" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H164" s="2"/>
-      <c r="I164" s="1"/>
-      <c r="J164" s="2"/>
-      <c r="K164" s="1"/>
+      <c r="B164" t="s">
+        <v>34</v>
+      </c>
+      <c r="C164">
+        <v>5755</v>
+      </c>
+      <c r="D164" t="s">
+        <v>56</v>
+      </c>
+      <c r="F164" t="s">
+        <v>31</v>
+      </c>
+      <c r="G164" t="s">
+        <v>13</v>
+      </c>
+      <c r="H164" s="2">
+        <v>0</v>
+      </c>
+      <c r="I164" s="1">
+        <v>46237.765162037038</v>
+      </c>
+      <c r="J164" s="2">
+        <v>0</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="165" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H165" s="2"/>
-      <c r="I165" s="1"/>
-      <c r="J165" s="2"/>
-      <c r="K165" s="1"/>
+      <c r="B165" t="s">
+        <v>34</v>
+      </c>
+      <c r="C165">
+        <v>2836</v>
+      </c>
+      <c r="D165" t="s">
+        <v>38</v>
+      </c>
+      <c r="F165" t="s">
+        <v>31</v>
+      </c>
+      <c r="G165" t="s">
+        <v>13</v>
+      </c>
+      <c r="H165" s="2">
+        <v>0</v>
+      </c>
+      <c r="I165" s="1">
+        <v>46237.765856481485</v>
+      </c>
+      <c r="J165" s="2">
+        <v>0</v>
+      </c>
+      <c r="K165" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="166" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H166" s="2"/>
-      <c r="I166" s="1"/>
-      <c r="J166" s="2"/>
-      <c r="K166" s="1"/>
+      <c r="B166" t="s">
+        <v>34</v>
+      </c>
+      <c r="C166">
+        <v>2755</v>
+      </c>
+      <c r="D166" t="s">
+        <v>40</v>
+      </c>
+      <c r="F166" t="s">
+        <v>31</v>
+      </c>
+      <c r="G166" t="s">
+        <v>13</v>
+      </c>
+      <c r="H166" s="2">
+        <v>0</v>
+      </c>
+      <c r="I166" s="1">
+        <v>46237.766550925924</v>
+      </c>
+      <c r="J166" s="2">
+        <v>0</v>
+      </c>
+      <c r="K166" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="167" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H167" s="2"/>
-      <c r="I167" s="1"/>
-      <c r="J167" s="2"/>
-      <c r="K167" s="1"/>
+      <c r="B167" t="s">
+        <v>34</v>
+      </c>
+      <c r="C167">
+        <v>2907</v>
+      </c>
+      <c r="D167" t="s">
+        <v>44</v>
+      </c>
+      <c r="F167" t="s">
+        <v>31</v>
+      </c>
+      <c r="G167" t="s">
+        <v>13</v>
+      </c>
+      <c r="H167" s="2">
+        <v>0</v>
+      </c>
+      <c r="I167" s="1">
+        <v>46237.766550925924</v>
+      </c>
+      <c r="J167" s="2">
+        <v>0</v>
+      </c>
+      <c r="K167" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="168" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H168" s="2"/>
@@ -46324,6 +46465,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -46338,11 +46480,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -46353,10 +46497,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -46374,14 +46521,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -46392,14 +46542,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -46426,6 +46579,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -46434,6 +46588,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -46446,22 +46601,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -46480,6 +46640,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -46490,10 +46651,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -46502,10 +46665,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -46519,82 +46684,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -46608,6 +46788,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -46618,6 +46799,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -46625,6 +46807,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -46633,86 +46816,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -46729,26 +46925,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -46779,6 +46981,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -46788,10 +46991,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -46804,14 +47009,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -46820,14 +47028,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -46846,26 +47057,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -46884,6 +47101,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -46892,10 +47110,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -46904,6 +47124,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -46916,10 +47137,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -46928,6 +47151,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -46936,14 +47160,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -46952,14 +47179,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -46976,76 +47206,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -47059,31 +47298,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -47096,10 +47342,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -47108,10 +47356,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -47120,6 +47370,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -47134,10 +47385,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -47146,10 +47399,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -47163,6 +47418,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -47178,14 +47434,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -47203,14 +47462,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -47223,10 +47485,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -47235,14 +47499,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -47251,10 +47518,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -47263,14 +47532,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -47292,6 +47564,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -47300,39 +47573,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Five-Aces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{280C9999-F605-4766-B8C6-6A903720F89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AC26E2D-8FE9-459B-B69F-2FB3D8756F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -583,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -659,7 +659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>34</v>
       </c>
@@ -833,7 +833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>34</v>
       </c>
@@ -949,7 +949,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>34</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>34</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>34</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>34</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>34</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>34</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>34</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>34</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>34</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>34</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>34</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>46237.764467592591</v>
       </c>
       <c r="J162" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K162" s="1" t="s">
         <v>11</v>
@@ -5217,7 +5217,7 @@
         <v>46237.764467592591</v>
       </c>
       <c r="J163" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K163" s="1" t="s">
         <v>11</v>
@@ -5246,7 +5246,7 @@
         <v>46237.765162037038</v>
       </c>
       <c r="J164" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K164" s="1" t="s">
         <v>11</v>
@@ -5275,7 +5275,7 @@
         <v>46237.765856481485</v>
       </c>
       <c r="J165" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K165" s="1" t="s">
         <v>11</v>
@@ -5304,7 +5304,7 @@
         <v>46237.766550925924</v>
       </c>
       <c r="J166" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K166" s="1" t="s">
         <v>11</v>
@@ -5333,7 +5333,7 @@
         <v>46237.766550925924</v>
       </c>
       <c r="J167" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K167" s="1" t="s">
         <v>11</v>
@@ -5375,7 +5375,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -5405,7 +5405,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -5465,7 +5465,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -5573,7 +5573,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -5765,7 +5765,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -6281,7 +6281,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -6347,7 +6347,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -6359,7 +6359,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -6455,7 +6455,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -6467,7 +6467,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -6563,7 +6563,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -6623,7 +6623,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -45576,6 +45576,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -45868,6 +45869,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -46178,6 +46181,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -46302,6 +46306,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -46313,6 +46318,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46461,6 +46467,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -46471,10 +46478,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -46508,15 +46517,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -46557,18 +46569,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46584,6 +46600,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -46593,10 +46610,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -46632,10 +46651,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -46661,6 +46682,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -46675,6 +46697,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46709,6 +46732,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -46718,6 +46742,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -46727,6 +46752,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -46741,15 +46767,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -46779,6 +46806,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -46799,11 +46827,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -46812,6 +46842,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -46841,6 +46872,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -46850,10 +46882,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -46868,14 +46902,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -46895,10 +46932,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -46918,9 +46957,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -46955,18 +46997,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -46981,12 +47027,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -47001,10 +47047,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -47024,6 +47072,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -47043,6 +47092,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -47052,6 +47102,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -47097,6 +47148,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -47106,6 +47158,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -47120,6 +47173,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -47129,10 +47183,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -47147,6 +47203,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -47156,6 +47213,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -47175,6 +47233,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -47194,10 +47253,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -47207,6 +47268,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -47217,10 +47279,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -47235,18 +47299,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -47266,10 +47334,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -47289,6 +47359,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -47319,7 +47390,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -47334,10 +47404,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -47352,6 +47424,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -47366,11 +47439,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -47380,6 +47453,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -47395,6 +47469,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -47409,6 +47484,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -47429,6 +47505,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -47454,11 +47531,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -47477,15 +47556,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -47495,6 +47575,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -47514,6 +47595,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -47528,6 +47610,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -47547,10 +47630,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47560,6 +47645,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -47570,6 +47656,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -47606,7 +47693,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -47615,6 +47701,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -47628,10 +47715,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Five-Aces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AC26E2D-8FE9-459B-B69F-2FB3D8756F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{934E1643-8A42-4CE3-A7B8-3199C1CCB913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -583,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -659,7 +659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>34</v>
       </c>
@@ -833,7 +833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>34</v>
       </c>
@@ -949,7 +949,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>34</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>34</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>34</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>34</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>34</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>34</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>34</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>34</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>34</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>34</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>34</v>
       </c>
@@ -5375,7 +5375,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
       <c r="J174" s="2"/>
@@ -5405,7 +5405,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="1"/>
     </row>
-    <row r="179" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
@@ -5465,7 +5465,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -5573,7 +5573,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -5765,7 +5765,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -6281,7 +6281,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -6347,7 +6347,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -6359,7 +6359,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -6455,7 +6455,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -6467,7 +6467,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -6563,7 +6563,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -6623,7 +6623,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -45576,7 +45576,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -45869,8 +45868,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -46181,7 +46178,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -46306,7 +46302,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -46318,7 +46313,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46467,35 +46461,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -46506,44 +46494,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -46554,37 +46533,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46595,52 +46567,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -46651,17 +46613,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -46672,32 +46631,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46707,106 +46660,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -46816,7 +46749,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -46827,127 +46759,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -46957,62 +46863,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -47032,67 +46925,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -47102,38 +46982,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -47148,117 +47021,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -47267,99 +47117,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -47369,23 +47200,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -47394,52 +47221,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -47453,38 +47270,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -47494,7 +47304,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -47505,23 +47314,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -47531,37 +47336,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -47570,72 +47368,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47645,76 +47429,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Five-Aces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{934E1643-8A42-4CE3-A7B8-3199C1CCB913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EDD219F-0571-48BD-86C1-B960F2964612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -583,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -45576,6 +45576,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -45868,6 +45869,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -46178,6 +46181,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -46302,6 +46306,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -46313,6 +46318,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46461,29 +46467,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -46494,35 +46506,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -46533,30 +46554,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46567,42 +46595,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -46613,14 +46651,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -46631,26 +46672,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46660,86 +46707,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -46749,6 +46817,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -46759,101 +46828,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -46863,49 +46958,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -46920,59 +47028,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -46982,31 +47104,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -47016,99 +47145,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -47117,80 +47270,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -47200,67 +47372,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -47270,31 +47458,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -47304,6 +47499,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -47314,19 +47510,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -47336,90 +47536,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47429,51 +47651,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
